--- a/DataRepo/tests/data/study_doc_versions/study_v3.xlsx
+++ b/DataRepo/tests/data/study_doc_versions/study_v3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-LOCAL/TRACEBASE/tracebase/DataRepo/data/tests/study_doc_versions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-local/TRACEBASE/tracebase/DataRepo/tests/data/study_doc_versions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94551C4-AFB8-4C4E-8A67-DB1A44C2D82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB6669FF-41AD-FF4F-A373-0AE26AFE7640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5600" yWindow="7700" windowWidth="38360" windowHeight="13720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5600" yWindow="7700" windowWidth="38360" windowHeight="13720" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study" sheetId="5" r:id="rId1"/>
@@ -710,12 +710,6 @@
     <t>BCAAs (VLI) {valine-[13C5,15N1][20]; leucine-[13C6,15N1][24]; isoleucine-[13C6,15N1][12]}</t>
   </si>
   <si>
-    <t>DataRepo/data/tests/study_doc_versions/glnfasted1_cor.xlsx</t>
-  </si>
-  <si>
-    <t>DataRepo/data/tests/study_doc_versions/alafasted_cor.xlsx</t>
-  </si>
-  <si>
     <t>no manipulation besides what is already described in other fields</t>
   </si>
   <si>
@@ -738,6 +732,12 @@
   </si>
   <si>
     <t>Sequence</t>
+  </si>
+  <si>
+    <t>DataRepo/tests/data/study_doc_versions/glnfasted1_cor.xlsx</t>
+  </si>
+  <si>
+    <t>DataRepo/tests/data/study_doc_versions/alafasted_cor.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1602,7 +1602,7 @@
         <v>87</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2926,7 +2926,7 @@
         <v>25</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.15">
@@ -2967,7 +2967,7 @@
     </row>
     <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>160</v>
@@ -2989,7 +2989,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" s="19" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>159</v>
@@ -3000,7 +3000,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A5" s="19" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>193</v>
@@ -3011,7 +3011,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A6" s="19" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>158</v>
@@ -3297,7 +3297,7 @@
         <v>90</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>92</v>
@@ -12972,7 +12972,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A1" s="23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>160</v>
@@ -13048,12 +13048,12 @@
         <v>201</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>220</v>
+      <c r="A2" s="15" t="s">
+        <v>228</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>173</v>
@@ -13064,7 +13064,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" s="15" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>173</v>
@@ -13117,7 +13117,7 @@
         <v>162</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>176</v>
@@ -13285,7 +13285,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
